--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.00282534693332</v>
+        <v>6.662959118876665</v>
       </c>
       <c r="D2" t="n">
-        <v>41.70955029526338</v>
+        <v>6.777801922980299</v>
       </c>
       <c r="E2" t="n">
-        <v>7.139420033942466</v>
+        <v>1.16015575551565</v>
       </c>
       <c r="F2" t="n">
-        <v>13.2352929197503</v>
+        <v>2.150735099459424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.33515387699358</v>
+        <v>6.229462505011457</v>
       </c>
       <c r="D3" t="n">
-        <v>22.06463688065621</v>
+        <v>3.585503493106635</v>
       </c>
       <c r="E3" t="n">
-        <v>7.139420033942466</v>
+        <v>1.16015575551565</v>
       </c>
       <c r="F3" t="n">
-        <v>13.2352929197503</v>
+        <v>2.150735099459424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.63674093242297</v>
+        <v>8.878470401518733</v>
       </c>
       <c r="D4" t="n">
-        <v>54.22174014262026</v>
+        <v>8.811032773175793</v>
       </c>
       <c r="E4" t="n">
-        <v>7.139420033942466</v>
+        <v>1.16015575551565</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2352929197503</v>
+        <v>2.150735099459424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
